--- a/day_5Excel+LAB+4+Dataset_Dmart.xlsx
+++ b/day_5Excel+LAB+4+Dataset_Dmart.xlsx
@@ -5,18 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AA7D5A-84D0-474C-8D1F-6011FF737266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C1BEFF-1AD8-472A-A110-FCA93A5B8228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
@@ -1773,15 +1784,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD86DCD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2157,32 +2160,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}" name="DMart_Sales_Table" displayName="DMart_Sales_Table" ref="A1:P499" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20">
-  <autoFilter ref="A1:P499" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}">
-    <filterColumn colId="4">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}" name="DMart_Sales_Table" displayName="DMart_Sales_Table" ref="A1:P499" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+  <autoFilter ref="A1:P499" xr:uid="{633466E1-73B5-4359-AC07-1E52788E9B23}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P499">
     <sortCondition descending="1" ref="E1:E499"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F5E12D93-0106-45F5-85DC-E8B1F8D53101}" name="Column1" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{14CC4549-ABDD-4DF7-B22B-1171582C1EB5}" name="Update_region" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{73F60E5C-6410-4EBC-BF8F-48147ED2B06D}" name="Region" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{5601AE86-639E-4ECB-8F37-EDEFA0C621B2}" name="Category" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{18189A26-37C2-4876-9484-BEBC1AF8C1D8}" name="sales" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{14F99767-DBCE-4AC8-8259-97A59E1EB21C}" name="discount" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{DBE0F0B5-C83B-4F9F-BBC9-FA335DF75EE9}" name="quantity" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{AA8C96D2-0B1B-452D-8572-5BCBBE0495E8}" name="order_date" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{69FB3965-E9D4-4A59-9D12-1AE18D3E43CA}" name="delivery_date" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{994325DC-9A01-43E7-96B5-20D7ED627202}" name="customer_type" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{C41D40E6-7D82-473E-BE13-9FD9311B0CCB}" name="customer_type2" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{F1EE67FC-2DD9-4BA1-8241-EA212EF984BD}" name="payment_mode" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{63A44F88-01FF-4BB3-ABA5-BEE30D42E51C}" name="profit" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{C6E2D886-D72C-4D61-B19E-82E2E3535F60}" name="Update_city" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{67B83AEA-1E76-4A42-A260-2804A8AB3C31}" name="Column2" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{C9894995-1ABD-4C38-9573-DD7C755DF436}" name="city" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{F5E12D93-0106-45F5-85DC-E8B1F8D53101}" name="Column1" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{14CC4549-ABDD-4DF7-B22B-1171582C1EB5}" name="Update_region" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{73F60E5C-6410-4EBC-BF8F-48147ED2B06D}" name="Region" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{5601AE86-639E-4ECB-8F37-EDEFA0C621B2}" name="Category" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{18189A26-37C2-4876-9484-BEBC1AF8C1D8}" name="sales" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{14F99767-DBCE-4AC8-8259-97A59E1EB21C}" name="discount" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{DBE0F0B5-C83B-4F9F-BBC9-FA335DF75EE9}" name="quantity" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{AA8C96D2-0B1B-452D-8572-5BCBBE0495E8}" name="order_date" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{69FB3965-E9D4-4A59-9D12-1AE18D3E43CA}" name="delivery_date" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{994325DC-9A01-43E7-96B5-20D7ED627202}" name="customer_type" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{C41D40E6-7D82-473E-BE13-9FD9311B0CCB}" name="customer_type2" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{F1EE67FC-2DD9-4BA1-8241-EA212EF984BD}" name="payment_mode" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{63A44F88-01FF-4BB3-ABA5-BEE30D42E51C}" name="profit" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{C6E2D886-D72C-4D61-B19E-82E2E3535F60}" name="Update_city" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{67B83AEA-1E76-4A42-A260-2804A8AB3C31}" name="Column2" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{C9894995-1ABD-4C38-9573-DD7C755DF436}" name="city" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3081,7 +3080,7 @@
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
     </row>
-    <row r="12" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>167</v>
       </c>
@@ -3142,7 +3141,7 @@
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
     </row>
-    <row r="13" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>125</v>
       </c>
@@ -3203,7 +3202,7 @@
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
     </row>
-    <row r="14" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>184</v>
       </c>
@@ -3264,7 +3263,7 @@
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
     </row>
-    <row r="15" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>148</v>
       </c>
@@ -3325,7 +3324,7 @@
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
     </row>
-    <row r="16" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>530</v>
       </c>
@@ -3386,7 +3385,7 @@
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
     </row>
-    <row r="17" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>515</v>
       </c>
@@ -3447,7 +3446,7 @@
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
     </row>
-    <row r="18" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>164</v>
       </c>
@@ -3508,7 +3507,7 @@
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
     </row>
-    <row r="19" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>63</v>
       </c>
@@ -3569,7 +3568,7 @@
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
     </row>
-    <row r="20" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>91</v>
       </c>
@@ -3630,7 +3629,7 @@
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
     </row>
-    <row r="21" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>414</v>
       </c>
@@ -3691,7 +3690,7 @@
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
     </row>
-    <row r="22" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>141</v>
       </c>
@@ -3752,7 +3751,7 @@
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
     </row>
-    <row r="23" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>512</v>
       </c>
@@ -3813,7 +3812,7 @@
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
     </row>
-    <row r="24" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
@@ -3874,7 +3873,7 @@
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
     </row>
-    <row r="25" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>130</v>
       </c>
@@ -3935,7 +3934,7 @@
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
     </row>
-    <row r="26" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>392</v>
       </c>
@@ -3996,7 +3995,7 @@
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
     </row>
-    <row r="27" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>103</v>
       </c>
@@ -4057,7 +4056,7 @@
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
     </row>
-    <row r="28" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>109</v>
       </c>
@@ -4118,7 +4117,7 @@
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
     </row>
-    <row r="29" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>102</v>
       </c>
@@ -4179,7 +4178,7 @@
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
     </row>
-    <row r="30" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>140</v>
       </c>
@@ -4240,7 +4239,7 @@
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
     </row>
-    <row r="31" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>361</v>
       </c>
@@ -4301,7 +4300,7 @@
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
     </row>
-    <row r="32" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>373</v>
       </c>
@@ -4362,7 +4361,7 @@
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
     </row>
-    <row r="33" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>377</v>
       </c>
@@ -4423,7 +4422,7 @@
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
     </row>
-    <row r="34" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>483</v>
       </c>
@@ -4484,7 +4483,7 @@
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
     </row>
-    <row r="35" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>250</v>
       </c>
@@ -4545,7 +4544,7 @@
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
     </row>
-    <row r="36" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>501</v>
       </c>
@@ -4606,7 +4605,7 @@
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
     </row>
-    <row r="37" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>353</v>
       </c>
@@ -4667,7 +4666,7 @@
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
     </row>
-    <row r="38" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>274</v>
       </c>
@@ -4728,7 +4727,7 @@
       <c r="AB38" s="2"/>
       <c r="AC38" s="2"/>
     </row>
-    <row r="39" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>465</v>
       </c>
@@ -4789,7 +4788,7 @@
       <c r="AB39" s="2"/>
       <c r="AC39" s="2"/>
     </row>
-    <row r="40" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>233</v>
       </c>
@@ -4850,7 +4849,7 @@
       <c r="AB40" s="2"/>
       <c r="AC40" s="2"/>
     </row>
-    <row r="41" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>261</v>
       </c>
@@ -4911,7 +4910,7 @@
       <c r="AB41" s="2"/>
       <c r="AC41" s="2"/>
     </row>
-    <row r="42" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>320</v>
       </c>
@@ -4972,7 +4971,7 @@
       <c r="AB42" s="2"/>
       <c r="AC42" s="2"/>
     </row>
-    <row r="43" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>352</v>
       </c>
@@ -5033,7 +5032,7 @@
       <c r="AB43" s="2"/>
       <c r="AC43" s="2"/>
     </row>
-    <row r="44" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>307</v>
       </c>
@@ -5094,7 +5093,7 @@
       <c r="AB44" s="2"/>
       <c r="AC44" s="2"/>
     </row>
-    <row r="45" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>538</v>
       </c>
@@ -5155,7 +5154,7 @@
       <c r="AB45" s="2"/>
       <c r="AC45" s="2"/>
     </row>
-    <row r="46" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>171</v>
       </c>
@@ -5216,7 +5215,7 @@
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
     </row>
-    <row r="47" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>133</v>
       </c>
@@ -5277,7 +5276,7 @@
       <c r="AB47" s="2"/>
       <c r="AC47" s="2"/>
     </row>
-    <row r="48" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>62</v>
       </c>
@@ -5338,7 +5337,7 @@
       <c r="AB48" s="2"/>
       <c r="AC48" s="2"/>
     </row>
-    <row r="49" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>190</v>
       </c>
@@ -5399,7 +5398,7 @@
       <c r="AB49" s="2"/>
       <c r="AC49" s="2"/>
     </row>
-    <row r="50" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>146</v>
       </c>
@@ -5460,7 +5459,7 @@
       <c r="AB50" s="2"/>
       <c r="AC50" s="2"/>
     </row>
-    <row r="51" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>475</v>
       </c>
@@ -5521,7 +5520,7 @@
       <c r="AB51" s="2"/>
       <c r="AC51" s="2"/>
     </row>
-    <row r="52" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>211</v>
       </c>
@@ -5582,7 +5581,7 @@
       <c r="AB52" s="2"/>
       <c r="AC52" s="2"/>
     </row>
-    <row r="53" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>214</v>
       </c>
@@ -5643,7 +5642,7 @@
       <c r="AB53" s="2"/>
       <c r="AC53" s="2"/>
     </row>
-    <row r="54" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>510</v>
       </c>
@@ -5704,7 +5703,7 @@
       <c r="AB54" s="2"/>
       <c r="AC54" s="2"/>
     </row>
-    <row r="55" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>235</v>
       </c>
@@ -5765,7 +5764,7 @@
       <c r="AB55" s="2"/>
       <c r="AC55" s="2"/>
     </row>
-    <row r="56" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>315</v>
       </c>
@@ -5826,7 +5825,7 @@
       <c r="AB56" s="2"/>
       <c r="AC56" s="2"/>
     </row>
-    <row r="57" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>61</v>
       </c>
@@ -5887,7 +5886,7 @@
       <c r="AB57" s="2"/>
       <c r="AC57" s="2"/>
     </row>
-    <row r="58" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>160</v>
       </c>
@@ -5948,7 +5947,7 @@
       <c r="AB58" s="2"/>
       <c r="AC58" s="2"/>
     </row>
-    <row r="59" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>135</v>
       </c>
@@ -6009,7 +6008,7 @@
       <c r="AB59" s="2"/>
       <c r="AC59" s="2"/>
     </row>
-    <row r="60" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>50</v>
       </c>
@@ -6070,7 +6069,7 @@
       <c r="AB60" s="2"/>
       <c r="AC60" s="2"/>
     </row>
-    <row r="61" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>327</v>
       </c>
@@ -6131,7 +6130,7 @@
       <c r="AB61" s="2"/>
       <c r="AC61" s="2"/>
     </row>
-    <row r="62" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>194</v>
       </c>
@@ -6192,7 +6191,7 @@
       <c r="AB62" s="2"/>
       <c r="AC62" s="2"/>
     </row>
-    <row r="63" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>342</v>
       </c>
@@ -6253,7 +6252,7 @@
       <c r="AB63" s="2"/>
       <c r="AC63" s="2"/>
     </row>
-    <row r="64" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>172</v>
       </c>
@@ -6314,7 +6313,7 @@
       <c r="AB64" s="2"/>
       <c r="AC64" s="2"/>
     </row>
-    <row r="65" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>459</v>
       </c>
@@ -6375,7 +6374,7 @@
       <c r="AB65" s="2"/>
       <c r="AC65" s="2"/>
     </row>
-    <row r="66" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>117</v>
       </c>
@@ -6436,7 +6435,7 @@
       <c r="AB66" s="2"/>
       <c r="AC66" s="2"/>
     </row>
-    <row r="67" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>406</v>
       </c>
@@ -6497,7 +6496,7 @@
       <c r="AB67" s="2"/>
       <c r="AC67" s="2"/>
     </row>
-    <row r="68" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>470</v>
       </c>
@@ -6558,7 +6557,7 @@
       <c r="AB68" s="2"/>
       <c r="AC68" s="2"/>
     </row>
-    <row r="69" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>81</v>
       </c>
@@ -6619,7 +6618,7 @@
       <c r="AB69" s="2"/>
       <c r="AC69" s="2"/>
     </row>
-    <row r="70" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>474</v>
       </c>
@@ -6680,7 +6679,7 @@
       <c r="AB70" s="2"/>
       <c r="AC70" s="2"/>
     </row>
-    <row r="71" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>500</v>
       </c>
@@ -6741,7 +6740,7 @@
       <c r="AB71" s="2"/>
       <c r="AC71" s="2"/>
     </row>
-    <row r="72" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>519</v>
       </c>
@@ -6802,7 +6801,7 @@
       <c r="AB72" s="2"/>
       <c r="AC72" s="2"/>
     </row>
-    <row r="73" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>276</v>
       </c>
@@ -6863,7 +6862,7 @@
       <c r="AB73" s="2"/>
       <c r="AC73" s="2"/>
     </row>
-    <row r="74" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>248</v>
       </c>
@@ -6924,7 +6923,7 @@
       <c r="AB74" s="2"/>
       <c r="AC74" s="2"/>
     </row>
-    <row r="75" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>219</v>
       </c>
@@ -6985,7 +6984,7 @@
       <c r="AB75" s="2"/>
       <c r="AC75" s="2"/>
     </row>
-    <row r="76" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>151</v>
       </c>
@@ -7046,7 +7045,7 @@
       <c r="AB76" s="2"/>
       <c r="AC76" s="2"/>
     </row>
-    <row r="77" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>367</v>
       </c>
@@ -7107,7 +7106,7 @@
       <c r="AB77" s="2"/>
       <c r="AC77" s="2"/>
     </row>
-    <row r="78" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>525</v>
       </c>
@@ -7168,7 +7167,7 @@
       <c r="AB78" s="2"/>
       <c r="AC78" s="2"/>
     </row>
-    <row r="79" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>441</v>
       </c>
@@ -7229,7 +7228,7 @@
       <c r="AB79" s="2"/>
       <c r="AC79" s="2"/>
     </row>
-    <row r="80" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>110</v>
       </c>
@@ -7290,7 +7289,7 @@
       <c r="AB80" s="2"/>
       <c r="AC80" s="2"/>
     </row>
-    <row r="81" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>466</v>
       </c>
@@ -7351,7 +7350,7 @@
       <c r="AB81" s="2"/>
       <c r="AC81" s="2"/>
     </row>
-    <row r="82" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>165</v>
       </c>
@@ -7412,7 +7411,7 @@
       <c r="AB82" s="2"/>
       <c r="AC82" s="2"/>
     </row>
-    <row r="83" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>268</v>
       </c>
@@ -7473,7 +7472,7 @@
       <c r="AB83" s="2"/>
       <c r="AC83" s="2"/>
     </row>
-    <row r="84" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>300</v>
       </c>
@@ -7534,7 +7533,7 @@
       <c r="AB84" s="2"/>
       <c r="AC84" s="2"/>
     </row>
-    <row r="85" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>196</v>
       </c>
@@ -7595,7 +7594,7 @@
       <c r="AB85" s="2"/>
       <c r="AC85" s="2"/>
     </row>
-    <row r="86" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>244</v>
       </c>
@@ -7656,7 +7655,7 @@
       <c r="AB86" s="2"/>
       <c r="AC86" s="2"/>
     </row>
-    <row r="87" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>527</v>
       </c>
@@ -7717,7 +7716,7 @@
       <c r="AB87" s="2"/>
       <c r="AC87" s="2"/>
     </row>
-    <row r="88" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>207</v>
       </c>
@@ -7778,7 +7777,7 @@
       <c r="AB88" s="2"/>
       <c r="AC88" s="2"/>
     </row>
-    <row r="89" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>287</v>
       </c>
@@ -7839,7 +7838,7 @@
       <c r="AB89" s="2"/>
       <c r="AC89" s="2"/>
     </row>
-    <row r="90" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>502</v>
       </c>
@@ -7900,7 +7899,7 @@
       <c r="AB90" s="2"/>
       <c r="AC90" s="2"/>
     </row>
-    <row r="91" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>439</v>
       </c>
@@ -7961,7 +7960,7 @@
       <c r="AB91" s="2"/>
       <c r="AC91" s="2"/>
     </row>
-    <row r="92" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>265</v>
       </c>
@@ -8022,7 +8021,7 @@
       <c r="AB92" s="2"/>
       <c r="AC92" s="2"/>
     </row>
-    <row r="93" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>153</v>
       </c>
@@ -8083,7 +8082,7 @@
       <c r="AB93" s="2"/>
       <c r="AC93" s="2"/>
     </row>
-    <row r="94" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>376</v>
       </c>
@@ -8144,7 +8143,7 @@
       <c r="AB94" s="2"/>
       <c r="AC94" s="2"/>
     </row>
-    <row r="95" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>46</v>
       </c>
@@ -8205,7 +8204,7 @@
       <c r="AB95" s="2"/>
       <c r="AC95" s="2"/>
     </row>
-    <row r="96" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>399</v>
       </c>
@@ -8266,7 +8265,7 @@
       <c r="AB96" s="2"/>
       <c r="AC96" s="2"/>
     </row>
-    <row r="97" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>485</v>
       </c>
@@ -8327,7 +8326,7 @@
       <c r="AB97" s="2"/>
       <c r="AC97" s="2"/>
     </row>
-    <row r="98" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>155</v>
       </c>
@@ -8388,7 +8387,7 @@
       <c r="AB98" s="2"/>
       <c r="AC98" s="2"/>
     </row>
-    <row r="99" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>482</v>
       </c>
@@ -8449,7 +8448,7 @@
       <c r="AB99" s="2"/>
       <c r="AC99" s="2"/>
     </row>
-    <row r="100" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>488</v>
       </c>
@@ -8510,7 +8509,7 @@
       <c r="AB100" s="2"/>
       <c r="AC100" s="2"/>
     </row>
-    <row r="101" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>535</v>
       </c>
@@ -8571,7 +8570,7 @@
       <c r="AB101" s="2"/>
       <c r="AC101" s="2"/>
     </row>
-    <row r="102" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>243</v>
       </c>
@@ -8632,7 +8631,7 @@
       <c r="AB102" s="2"/>
       <c r="AC102" s="2"/>
     </row>
-    <row r="103" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>301</v>
       </c>
@@ -8693,7 +8692,7 @@
       <c r="AB103" s="2"/>
       <c r="AC103" s="2"/>
     </row>
-    <row r="104" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>462</v>
       </c>
@@ -8754,7 +8753,7 @@
       <c r="AB104" s="2"/>
       <c r="AC104" s="2"/>
     </row>
-    <row r="105" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>142</v>
       </c>
@@ -8815,7 +8814,7 @@
       <c r="AB105" s="2"/>
       <c r="AC105" s="2"/>
     </row>
-    <row r="106" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>503</v>
       </c>
@@ -8876,7 +8875,7 @@
       <c r="AB106" s="2"/>
       <c r="AC106" s="2"/>
     </row>
-    <row r="107" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>362</v>
       </c>
@@ -8937,7 +8936,7 @@
       <c r="AB107" s="2"/>
       <c r="AC107" s="2"/>
     </row>
-    <row r="108" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>200</v>
       </c>
@@ -8998,7 +8997,7 @@
       <c r="AB108" s="2"/>
       <c r="AC108" s="2"/>
     </row>
-    <row r="109" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>120</v>
       </c>
@@ -9059,7 +9058,7 @@
       <c r="AB109" s="2"/>
       <c r="AC109" s="2"/>
     </row>
-    <row r="110" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>407</v>
       </c>
@@ -9120,7 +9119,7 @@
       <c r="AB110" s="2"/>
       <c r="AC110" s="2"/>
     </row>
-    <row r="111" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>239</v>
       </c>
@@ -9181,7 +9180,7 @@
       <c r="AB111" s="2"/>
       <c r="AC111" s="2"/>
     </row>
-    <row r="112" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>314</v>
       </c>
@@ -9242,7 +9241,7 @@
       <c r="AB112" s="2"/>
       <c r="AC112" s="2"/>
     </row>
-    <row r="113" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>348</v>
       </c>
@@ -9303,7 +9302,7 @@
       <c r="AB113" s="2"/>
       <c r="AC113" s="2"/>
     </row>
-    <row r="114" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>294</v>
       </c>
@@ -9364,7 +9363,7 @@
       <c r="AB114" s="2"/>
       <c r="AC114" s="2"/>
     </row>
-    <row r="115" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>58</v>
       </c>
@@ -9425,7 +9424,7 @@
       <c r="AB115" s="2"/>
       <c r="AC115" s="2"/>
     </row>
-    <row r="116" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>455</v>
       </c>
@@ -9486,7 +9485,7 @@
       <c r="AB116" s="2"/>
       <c r="AC116" s="2"/>
     </row>
-    <row r="117" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>92</v>
       </c>
@@ -9547,7 +9546,7 @@
       <c r="AB117" s="2"/>
       <c r="AC117" s="2"/>
     </row>
-    <row r="118" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>490</v>
       </c>
@@ -9608,7 +9607,7 @@
       <c r="AB118" s="2"/>
       <c r="AC118" s="2"/>
     </row>
-    <row r="119" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>426</v>
       </c>
@@ -9669,7 +9668,7 @@
       <c r="AB119" s="2"/>
       <c r="AC119" s="2"/>
     </row>
-    <row r="120" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>505</v>
       </c>
@@ -9730,7 +9729,7 @@
       <c r="AB120" s="2"/>
       <c r="AC120" s="2"/>
     </row>
-    <row r="121" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>55</v>
       </c>
@@ -9791,7 +9790,7 @@
       <c r="AB121" s="2"/>
       <c r="AC121" s="2"/>
     </row>
-    <row r="122" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>492</v>
       </c>
@@ -9852,7 +9851,7 @@
       <c r="AB122" s="2"/>
       <c r="AC122" s="2"/>
     </row>
-    <row r="123" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>415</v>
       </c>
@@ -9913,7 +9912,7 @@
       <c r="AB123" s="2"/>
       <c r="AC123" s="2"/>
     </row>
-    <row r="124" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>506</v>
       </c>
@@ -9974,7 +9973,7 @@
       <c r="AB124" s="2"/>
       <c r="AC124" s="2"/>
     </row>
-    <row r="125" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>112</v>
       </c>
@@ -10035,7 +10034,7 @@
       <c r="AB125" s="2"/>
       <c r="AC125" s="2"/>
     </row>
-    <row r="126" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>374</v>
       </c>
@@ -10096,7 +10095,7 @@
       <c r="AB126" s="2"/>
       <c r="AC126" s="2"/>
     </row>
-    <row r="127" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>467</v>
       </c>
@@ -10157,7 +10156,7 @@
       <c r="AB127" s="2"/>
       <c r="AC127" s="2"/>
     </row>
-    <row r="128" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>499</v>
       </c>
@@ -10218,7 +10217,7 @@
       <c r="AB128" s="2"/>
       <c r="AC128" s="2"/>
     </row>
-    <row r="129" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>226</v>
       </c>
@@ -10279,7 +10278,7 @@
       <c r="AB129" s="2"/>
       <c r="AC129" s="2"/>
     </row>
-    <row r="130" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>129</v>
       </c>
@@ -10340,7 +10339,7 @@
       <c r="AB130" s="2"/>
       <c r="AC130" s="2"/>
     </row>
-    <row r="131" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>65</v>
       </c>
@@ -10401,7 +10400,7 @@
       <c r="AB131" s="2"/>
       <c r="AC131" s="2"/>
     </row>
-    <row r="132" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>454</v>
       </c>
@@ -10462,7 +10461,7 @@
       <c r="AB132" s="2"/>
       <c r="AC132" s="2"/>
     </row>
-    <row r="133" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>460</v>
       </c>
@@ -10523,7 +10522,7 @@
       <c r="AB133" s="2"/>
       <c r="AC133" s="2"/>
     </row>
-    <row r="134" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>247</v>
       </c>
@@ -10584,7 +10583,7 @@
       <c r="AB134" s="2"/>
       <c r="AC134" s="2"/>
     </row>
-    <row r="135" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>208</v>
       </c>
@@ -10645,7 +10644,7 @@
       <c r="AB135" s="2"/>
       <c r="AC135" s="2"/>
     </row>
-    <row r="136" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>410</v>
       </c>
@@ -10706,7 +10705,7 @@
       <c r="AB136" s="2"/>
       <c r="AC136" s="2"/>
     </row>
-    <row r="137" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>435</v>
       </c>
@@ -10767,7 +10766,7 @@
       <c r="AB137" s="2"/>
       <c r="AC137" s="2"/>
     </row>
-    <row r="138" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>118</v>
       </c>
@@ -10828,7 +10827,7 @@
       <c r="AB138" s="2"/>
       <c r="AC138" s="2"/>
     </row>
-    <row r="139" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>282</v>
       </c>
@@ -10889,7 +10888,7 @@
       <c r="AB139" s="2"/>
       <c r="AC139" s="2"/>
     </row>
-    <row r="140" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>321</v>
       </c>
@@ -10950,7 +10949,7 @@
       <c r="AB140" s="2"/>
       <c r="AC140" s="2"/>
     </row>
-    <row r="141" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>295</v>
       </c>
@@ -11011,7 +11010,7 @@
       <c r="AB141" s="2"/>
       <c r="AC141" s="2"/>
     </row>
-    <row r="142" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>412</v>
       </c>
@@ -11072,7 +11071,7 @@
       <c r="AB142" s="2"/>
       <c r="AC142" s="2"/>
     </row>
-    <row r="143" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>182</v>
       </c>
@@ -11133,7 +11132,7 @@
       <c r="AB143" s="2"/>
       <c r="AC143" s="2"/>
     </row>
-    <row r="144" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>18</v>
       </c>
@@ -11194,7 +11193,7 @@
       <c r="AB144" s="2"/>
       <c r="AC144" s="2"/>
     </row>
-    <row r="145" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>328</v>
       </c>
@@ -11255,7 +11254,7 @@
       <c r="AB145" s="2"/>
       <c r="AC145" s="2"/>
     </row>
-    <row r="146" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>297</v>
       </c>
@@ -11316,7 +11315,7 @@
       <c r="AB146" s="2"/>
       <c r="AC146" s="2"/>
     </row>
-    <row r="147" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>526</v>
       </c>
@@ -11377,7 +11376,7 @@
       <c r="AB147" s="2"/>
       <c r="AC147" s="2"/>
     </row>
-    <row r="148" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>217</v>
       </c>
@@ -11438,7 +11437,7 @@
       <c r="AB148" s="2"/>
       <c r="AC148" s="2"/>
     </row>
-    <row r="149" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>54</v>
       </c>
@@ -11499,7 +11498,7 @@
       <c r="AB149" s="2"/>
       <c r="AC149" s="2"/>
     </row>
-    <row r="150" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>296</v>
       </c>
@@ -11560,7 +11559,7 @@
       <c r="AB150" s="2"/>
       <c r="AC150" s="2"/>
     </row>
-    <row r="151" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>201</v>
       </c>
@@ -11621,7 +11620,7 @@
       <c r="AB151" s="2"/>
       <c r="AC151" s="2"/>
     </row>
-    <row r="152" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>343</v>
       </c>
@@ -11682,7 +11681,7 @@
       <c r="AB152" s="2"/>
       <c r="AC152" s="2"/>
     </row>
-    <row r="153" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>477</v>
       </c>
@@ -11743,7 +11742,7 @@
       <c r="AB153" s="2"/>
       <c r="AC153" s="2"/>
     </row>
-    <row r="154" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>124</v>
       </c>
@@ -11804,7 +11803,7 @@
       <c r="AB154" s="2"/>
       <c r="AC154" s="2"/>
     </row>
-    <row r="155" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>402</v>
       </c>
@@ -11865,7 +11864,7 @@
       <c r="AB155" s="2"/>
       <c r="AC155" s="2"/>
     </row>
-    <row r="156" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>355</v>
       </c>
@@ -11926,7 +11925,7 @@
       <c r="AB156" s="2"/>
       <c r="AC156" s="2"/>
     </row>
-    <row r="157" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>424</v>
       </c>
@@ -11987,7 +11986,7 @@
       <c r="AB157" s="2"/>
       <c r="AC157" s="2"/>
     </row>
-    <row r="158" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>75</v>
       </c>
@@ -12048,7 +12047,7 @@
       <c r="AB158" s="2"/>
       <c r="AC158" s="2"/>
     </row>
-    <row r="159" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>170</v>
       </c>
@@ -12109,7 +12108,7 @@
       <c r="AB159" s="2"/>
       <c r="AC159" s="2"/>
     </row>
-    <row r="160" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>24</v>
       </c>
@@ -12170,7 +12169,7 @@
       <c r="AB160" s="2"/>
       <c r="AC160" s="2"/>
     </row>
-    <row r="161" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>68</v>
       </c>
@@ -12231,7 +12230,7 @@
       <c r="AB161" s="2"/>
       <c r="AC161" s="2"/>
     </row>
-    <row r="162" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>272</v>
       </c>
@@ -12292,7 +12291,7 @@
       <c r="AB162" s="2"/>
       <c r="AC162" s="2"/>
     </row>
-    <row r="163" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>264</v>
       </c>
@@ -12353,7 +12352,7 @@
       <c r="AB163" s="2"/>
       <c r="AC163" s="2"/>
     </row>
-    <row r="164" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>334</v>
       </c>
@@ -12414,7 +12413,7 @@
       <c r="AB164" s="2"/>
       <c r="AC164" s="2"/>
     </row>
-    <row r="165" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>169</v>
       </c>
@@ -12475,7 +12474,7 @@
       <c r="AB165" s="2"/>
       <c r="AC165" s="2"/>
     </row>
-    <row r="166" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>511</v>
       </c>
@@ -12536,7 +12535,7 @@
       <c r="AB166" s="2"/>
       <c r="AC166" s="2"/>
     </row>
-    <row r="167" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>529</v>
       </c>
@@ -12597,7 +12596,7 @@
       <c r="AB167" s="2"/>
       <c r="AC167" s="2"/>
     </row>
-    <row r="168" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>84</v>
       </c>
@@ -12658,7 +12657,7 @@
       <c r="AB168" s="2"/>
       <c r="AC168" s="2"/>
     </row>
-    <row r="169" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>480</v>
       </c>
@@ -12719,7 +12718,7 @@
       <c r="AB169" s="2"/>
       <c r="AC169" s="2"/>
     </row>
-    <row r="170" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>388</v>
       </c>
@@ -12780,7 +12779,7 @@
       <c r="AB170" s="2"/>
       <c r="AC170" s="2"/>
     </row>
-    <row r="171" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>302</v>
       </c>
@@ -12841,7 +12840,7 @@
       <c r="AB171" s="2"/>
       <c r="AC171" s="2"/>
     </row>
-    <row r="172" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>116</v>
       </c>
@@ -12902,7 +12901,7 @@
       <c r="AB172" s="2"/>
       <c r="AC172" s="2"/>
     </row>
-    <row r="173" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>382</v>
       </c>
@@ -12963,7 +12962,7 @@
       <c r="AB173" s="2"/>
       <c r="AC173" s="2"/>
     </row>
-    <row r="174" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>254</v>
       </c>
@@ -13024,7 +13023,7 @@
       <c r="AB174" s="2"/>
       <c r="AC174" s="2"/>
     </row>
-    <row r="175" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>88</v>
       </c>
@@ -13085,7 +13084,7 @@
       <c r="AB175" s="2"/>
       <c r="AC175" s="2"/>
     </row>
-    <row r="176" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>344</v>
       </c>
@@ -13146,7 +13145,7 @@
       <c r="AB176" s="2"/>
       <c r="AC176" s="2"/>
     </row>
-    <row r="177" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>306</v>
       </c>
@@ -13207,7 +13206,7 @@
       <c r="AB177" s="2"/>
       <c r="AC177" s="2"/>
     </row>
-    <row r="178" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>537</v>
       </c>
@@ -13268,7 +13267,7 @@
       <c r="AB178" s="2"/>
       <c r="AC178" s="2"/>
     </row>
-    <row r="179" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>486</v>
       </c>
@@ -13329,7 +13328,7 @@
       <c r="AB179" s="2"/>
       <c r="AC179" s="2"/>
     </row>
-    <row r="180" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>508</v>
       </c>
@@ -13390,7 +13389,7 @@
       <c r="AB180" s="2"/>
       <c r="AC180" s="2"/>
     </row>
-    <row r="181" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>283</v>
       </c>
@@ -13451,7 +13450,7 @@
       <c r="AB181" s="2"/>
       <c r="AC181" s="2"/>
     </row>
-    <row r="182" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>79</v>
       </c>
@@ -13512,7 +13511,7 @@
       <c r="AB182" s="2"/>
       <c r="AC182" s="2"/>
     </row>
-    <row r="183" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>420</v>
       </c>
@@ -13573,7 +13572,7 @@
       <c r="AB183" s="2"/>
       <c r="AC183" s="2"/>
     </row>
-    <row r="184" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>476</v>
       </c>
@@ -13634,7 +13633,7 @@
       <c r="AB184" s="2"/>
       <c r="AC184" s="2"/>
     </row>
-    <row r="185" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>471</v>
       </c>
@@ -13695,7 +13694,7 @@
       <c r="AB185" s="2"/>
       <c r="AC185" s="2"/>
     </row>
-    <row r="186" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>60</v>
       </c>
@@ -13756,7 +13755,7 @@
       <c r="AB186" s="2"/>
       <c r="AC186" s="2"/>
     </row>
-    <row r="187" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>154</v>
       </c>
@@ -13817,7 +13816,7 @@
       <c r="AB187" s="2"/>
       <c r="AC187" s="2"/>
     </row>
-    <row r="188" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>422</v>
       </c>
@@ -13878,7 +13877,7 @@
       <c r="AB188" s="2"/>
       <c r="AC188" s="2"/>
     </row>
-    <row r="189" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>289</v>
       </c>
@@ -13939,7 +13938,7 @@
       <c r="AB189" s="2"/>
       <c r="AC189" s="2"/>
     </row>
-    <row r="190" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>443</v>
       </c>
@@ -14000,7 +13999,7 @@
       <c r="AB190" s="2"/>
       <c r="AC190" s="2"/>
     </row>
-    <row r="191" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>237</v>
       </c>
@@ -14061,7 +14060,7 @@
       <c r="AB191" s="2"/>
       <c r="AC191" s="2"/>
     </row>
-    <row r="192" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>52</v>
       </c>
@@ -14122,7 +14121,7 @@
       <c r="AB192" s="2"/>
       <c r="AC192" s="2"/>
     </row>
-    <row r="193" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>518</v>
       </c>
@@ -14183,7 +14182,7 @@
       <c r="AB193" s="2"/>
       <c r="AC193" s="2"/>
     </row>
-    <row r="194" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>398</v>
       </c>
@@ -14244,7 +14243,7 @@
       <c r="AB194" s="2"/>
       <c r="AC194" s="2"/>
     </row>
-    <row r="195" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>107</v>
       </c>
@@ -14305,7 +14304,7 @@
       <c r="AB195" s="2"/>
       <c r="AC195" s="2"/>
     </row>
-    <row r="196" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>174</v>
       </c>
@@ -14366,7 +14365,7 @@
       <c r="AB196" s="2"/>
       <c r="AC196" s="2"/>
     </row>
-    <row r="197" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>161</v>
       </c>
@@ -14427,7 +14426,7 @@
       <c r="AB197" s="2"/>
       <c r="AC197" s="2"/>
     </row>
-    <row r="198" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>215</v>
       </c>
@@ -14488,7 +14487,7 @@
       <c r="AB198" s="2"/>
       <c r="AC198" s="2"/>
     </row>
-    <row r="199" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>113</v>
       </c>
@@ -14549,7 +14548,7 @@
       <c r="AB199" s="2"/>
       <c r="AC199" s="2"/>
     </row>
-    <row r="200" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>157</v>
       </c>
@@ -14610,7 +14609,7 @@
       <c r="AB200" s="2"/>
       <c r="AC200" s="2"/>
     </row>
-    <row r="201" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>438</v>
       </c>
@@ -14671,7 +14670,7 @@
       <c r="AB201" s="2"/>
       <c r="AC201" s="2"/>
     </row>
-    <row r="202" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>266</v>
       </c>
@@ -14732,7 +14731,7 @@
       <c r="AB202" s="2"/>
       <c r="AC202" s="2"/>
     </row>
-    <row r="203" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>275</v>
       </c>
@@ -14793,7 +14792,7 @@
       <c r="AB203" s="2"/>
       <c r="AC203" s="2"/>
     </row>
-    <row r="204" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>249</v>
       </c>
@@ -14854,7 +14853,7 @@
       <c r="AB204" s="2"/>
       <c r="AC204" s="2"/>
     </row>
-    <row r="205" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>316</v>
       </c>
@@ -14915,7 +14914,7 @@
       <c r="AB205" s="2"/>
       <c r="AC205" s="2"/>
     </row>
-    <row r="206" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>450</v>
       </c>
@@ -14976,7 +14975,7 @@
       <c r="AB206" s="2"/>
       <c r="AC206" s="2"/>
     </row>
-    <row r="207" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>331</v>
       </c>
@@ -15037,7 +15036,7 @@
       <c r="AB207" s="2"/>
       <c r="AC207" s="2"/>
     </row>
-    <row r="208" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>139</v>
       </c>
@@ -15098,7 +15097,7 @@
       <c r="AB208" s="2"/>
       <c r="AC208" s="2"/>
     </row>
-    <row r="209" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>230</v>
       </c>
@@ -15159,7 +15158,7 @@
       <c r="AB209" s="2"/>
       <c r="AC209" s="2"/>
     </row>
-    <row r="210" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>105</v>
       </c>
@@ -15220,7 +15219,7 @@
       <c r="AB210" s="2"/>
       <c r="AC210" s="2"/>
     </row>
-    <row r="211" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>531</v>
       </c>
@@ -15281,7 +15280,7 @@
       <c r="AB211" s="2"/>
       <c r="AC211" s="2"/>
     </row>
-    <row r="212" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>181</v>
       </c>
@@ -15342,7 +15341,7 @@
       <c r="AB212" s="2"/>
       <c r="AC212" s="2"/>
     </row>
-    <row r="213" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>290</v>
       </c>
@@ -15403,7 +15402,7 @@
       <c r="AB213" s="2"/>
       <c r="AC213" s="2"/>
     </row>
-    <row r="214" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>32</v>
       </c>
@@ -15464,7 +15463,7 @@
       <c r="AB214" s="2"/>
       <c r="AC214" s="2"/>
     </row>
-    <row r="215" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>303</v>
       </c>
@@ -15525,7 +15524,7 @@
       <c r="AB215" s="2"/>
       <c r="AC215" s="2"/>
     </row>
-    <row r="216" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>271</v>
       </c>
@@ -15586,7 +15585,7 @@
       <c r="AB216" s="2"/>
       <c r="AC216" s="2"/>
     </row>
-    <row r="217" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>479</v>
       </c>
@@ -15647,7 +15646,7 @@
       <c r="AB217" s="2"/>
       <c r="AC217" s="2"/>
     </row>
-    <row r="218" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>221</v>
       </c>
@@ -15708,7 +15707,7 @@
       <c r="AB218" s="2"/>
       <c r="AC218" s="2"/>
     </row>
-    <row r="219" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>115</v>
       </c>
@@ -15769,7 +15768,7 @@
       <c r="AB219" s="2"/>
       <c r="AC219" s="2"/>
     </row>
-    <row r="220" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>369</v>
       </c>
@@ -15830,7 +15829,7 @@
       <c r="AB220" s="2"/>
       <c r="AC220" s="2"/>
     </row>
-    <row r="221" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>90</v>
       </c>
@@ -15891,7 +15890,7 @@
       <c r="AB221" s="2"/>
       <c r="AC221" s="2"/>
     </row>
-    <row r="222" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>364</v>
       </c>
@@ -15952,7 +15951,7 @@
       <c r="AB222" s="2"/>
       <c r="AC222" s="2"/>
     </row>
-    <row r="223" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>150</v>
       </c>
@@ -16013,7 +16012,7 @@
       <c r="AB223" s="2"/>
       <c r="AC223" s="2"/>
     </row>
-    <row r="224" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>357</v>
       </c>
@@ -16074,7 +16073,7 @@
       <c r="AB224" s="2"/>
       <c r="AC224" s="2"/>
     </row>
-    <row r="225" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>273</v>
       </c>
@@ -16135,7 +16134,7 @@
       <c r="AB225" s="2"/>
       <c r="AC225" s="2"/>
     </row>
-    <row r="226" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>186</v>
       </c>
@@ -16196,7 +16195,7 @@
       <c r="AB226" s="2"/>
       <c r="AC226" s="2"/>
     </row>
-    <row r="227" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>277</v>
       </c>
@@ -16257,7 +16256,7 @@
       <c r="AB227" s="2"/>
       <c r="AC227" s="2"/>
     </row>
-    <row r="228" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>187</v>
       </c>
@@ -16318,7 +16317,7 @@
       <c r="AB228" s="2"/>
       <c r="AC228" s="2"/>
     </row>
-    <row r="229" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>229</v>
       </c>
@@ -16379,7 +16378,7 @@
       <c r="AB229" s="2"/>
       <c r="AC229" s="2"/>
     </row>
-    <row r="230" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>487</v>
       </c>
@@ -16440,7 +16439,7 @@
       <c r="AB230" s="2"/>
       <c r="AC230" s="2"/>
     </row>
-    <row r="231" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>401</v>
       </c>
@@ -16501,7 +16500,7 @@
       <c r="AB231" s="2"/>
       <c r="AC231" s="2"/>
     </row>
-    <row r="232" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>119</v>
       </c>
@@ -16562,7 +16561,7 @@
       <c r="AB232" s="2"/>
       <c r="AC232" s="2"/>
     </row>
-    <row r="233" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>76</v>
       </c>
@@ -16623,7 +16622,7 @@
       <c r="AB233" s="2"/>
       <c r="AC233" s="2"/>
     </row>
-    <row r="234" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>446</v>
       </c>
@@ -16684,7 +16683,7 @@
       <c r="AB234" s="2"/>
       <c r="AC234" s="2"/>
     </row>
-    <row r="235" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>387</v>
       </c>
@@ -16745,7 +16744,7 @@
       <c r="AB235" s="2"/>
       <c r="AC235" s="2"/>
     </row>
-    <row r="236" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>100</v>
       </c>
@@ -16806,7 +16805,7 @@
       <c r="AB236" s="2"/>
       <c r="AC236" s="2"/>
     </row>
-    <row r="237" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>350</v>
       </c>
@@ -16867,7 +16866,7 @@
       <c r="AB237" s="2"/>
       <c r="AC237" s="2"/>
     </row>
-    <row r="238" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>78</v>
       </c>
@@ -16928,7 +16927,7 @@
       <c r="AB238" s="2"/>
       <c r="AC238" s="2"/>
     </row>
-    <row r="239" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>137</v>
       </c>
@@ -16989,7 +16988,7 @@
       <c r="AB239" s="2"/>
       <c r="AC239" s="2"/>
     </row>
-    <row r="240" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>417</v>
       </c>
@@ -17050,7 +17049,7 @@
       <c r="AB240" s="2"/>
       <c r="AC240" s="2"/>
     </row>
-    <row r="241" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>177</v>
       </c>
@@ -17111,7 +17110,7 @@
       <c r="AB241" s="2"/>
       <c r="AC241" s="2"/>
     </row>
-    <row r="242" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>436</v>
       </c>
@@ -17172,7 +17171,7 @@
       <c r="AB242" s="2"/>
       <c r="AC242" s="2"/>
     </row>
-    <row r="243" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>191</v>
       </c>
@@ -17233,7 +17232,7 @@
       <c r="AB243" s="2"/>
       <c r="AC243" s="2"/>
     </row>
-    <row r="244" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>216</v>
       </c>
@@ -17294,7 +17293,7 @@
       <c r="AB244" s="2"/>
       <c r="AC244" s="2"/>
     </row>
-    <row r="245" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>279</v>
       </c>
@@ -17355,7 +17354,7 @@
       <c r="AB245" s="2"/>
       <c r="AC245" s="2"/>
     </row>
-    <row r="246" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>539</v>
       </c>
@@ -17416,7 +17415,7 @@
       <c r="AB246" s="2"/>
       <c r="AC246" s="2"/>
     </row>
-    <row r="247" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>198</v>
       </c>
@@ -17477,7 +17476,7 @@
       <c r="AB247" s="2"/>
       <c r="AC247" s="2"/>
     </row>
-    <row r="248" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>220</v>
       </c>
@@ -17538,7 +17537,7 @@
       <c r="AB248" s="2"/>
       <c r="AC248" s="2"/>
     </row>
-    <row r="249" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>258</v>
       </c>
@@ -17599,7 +17598,7 @@
       <c r="AB249" s="2"/>
       <c r="AC249" s="2"/>
     </row>
-    <row r="250" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>213</v>
       </c>
@@ -17660,7 +17659,7 @@
       <c r="AB250" s="2"/>
       <c r="AC250" s="2"/>
     </row>
-    <row r="251" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>202</v>
       </c>
@@ -17721,7 +17720,7 @@
       <c r="AB251" s="2"/>
       <c r="AC251" s="2"/>
     </row>
-    <row r="252" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>212</v>
       </c>
@@ -17782,7 +17781,7 @@
       <c r="AB252" s="2"/>
       <c r="AC252" s="2"/>
     </row>
-    <row r="253" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>534</v>
       </c>
@@ -17843,7 +17842,7 @@
       <c r="AB253" s="2"/>
       <c r="AC253" s="2"/>
     </row>
-    <row r="254" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>138</v>
       </c>
@@ -17904,7 +17903,7 @@
       <c r="AB254" s="2"/>
       <c r="AC254" s="2"/>
     </row>
-    <row r="255" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>176</v>
       </c>
@@ -17965,7 +17964,7 @@
       <c r="AB255" s="2"/>
       <c r="AC255" s="2"/>
     </row>
-    <row r="256" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>522</v>
       </c>
@@ -18026,7 +18025,7 @@
       <c r="AB256" s="2"/>
       <c r="AC256" s="2"/>
     </row>
-    <row r="257" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>147</v>
       </c>
@@ -18087,7 +18086,7 @@
       <c r="AB257" s="2"/>
       <c r="AC257" s="2"/>
     </row>
-    <row r="258" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>337</v>
       </c>
@@ -18148,7 +18147,7 @@
       <c r="AB258" s="2"/>
       <c r="AC258" s="2"/>
     </row>
-    <row r="259" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>312</v>
       </c>
@@ -18209,7 +18208,7 @@
       <c r="AB259" s="2"/>
       <c r="AC259" s="2"/>
     </row>
-    <row r="260" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>269</v>
       </c>
@@ -18270,7 +18269,7 @@
       <c r="AB260" s="2"/>
       <c r="AC260" s="2"/>
     </row>
-    <row r="261" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>44</v>
       </c>
@@ -18331,7 +18330,7 @@
       <c r="AB261" s="2"/>
       <c r="AC261" s="2"/>
     </row>
-    <row r="262" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>451</v>
       </c>
@@ -18392,7 +18391,7 @@
       <c r="AB262" s="2"/>
       <c r="AC262" s="2"/>
     </row>
-    <row r="263" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>34</v>
       </c>
@@ -18453,7 +18452,7 @@
       <c r="AB263" s="2"/>
       <c r="AC263" s="2"/>
     </row>
-    <row r="264" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>323</v>
       </c>
@@ -18514,7 +18513,7 @@
       <c r="AB264" s="2"/>
       <c r="AC264" s="2"/>
     </row>
-    <row r="265" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>333</v>
       </c>
@@ -18575,7 +18574,7 @@
       <c r="AB265" s="2"/>
       <c r="AC265" s="2"/>
     </row>
-    <row r="266" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>131</v>
       </c>
@@ -18636,7 +18635,7 @@
       <c r="AB266" s="2"/>
       <c r="AC266" s="2"/>
     </row>
-    <row r="267" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>114</v>
       </c>
@@ -18697,7 +18696,7 @@
       <c r="AB267" s="2"/>
       <c r="AC267" s="2"/>
     </row>
-    <row r="268" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>145</v>
       </c>
@@ -18758,7 +18757,7 @@
       <c r="AB268" s="2"/>
       <c r="AC268" s="2"/>
     </row>
-    <row r="269" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>411</v>
       </c>
@@ -18819,7 +18818,7 @@
       <c r="AB269" s="2"/>
       <c r="AC269" s="2"/>
     </row>
-    <row r="270" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>317</v>
       </c>
@@ -18880,7 +18879,7 @@
       <c r="AB270" s="2"/>
       <c r="AC270" s="2"/>
     </row>
-    <row r="271" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>204</v>
       </c>
@@ -18941,7 +18940,7 @@
       <c r="AB271" s="2"/>
       <c r="AC271" s="2"/>
     </row>
-    <row r="272" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>447</v>
       </c>
@@ -19002,7 +19001,7 @@
       <c r="AB272" s="2"/>
       <c r="AC272" s="2"/>
     </row>
-    <row r="273" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>291</v>
       </c>
@@ -19063,7 +19062,7 @@
       <c r="AB273" s="2"/>
       <c r="AC273" s="2"/>
     </row>
-    <row r="274" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>94</v>
       </c>
@@ -19124,7 +19123,7 @@
       <c r="AB274" s="2"/>
       <c r="AC274" s="2"/>
     </row>
-    <row r="275" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>345</v>
       </c>
@@ -19185,7 +19184,7 @@
       <c r="AB275" s="2"/>
       <c r="AC275" s="2"/>
     </row>
-    <row r="276" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>523</v>
       </c>
@@ -19246,7 +19245,7 @@
       <c r="AB276" s="2"/>
       <c r="AC276" s="2"/>
     </row>
-    <row r="277" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>390</v>
       </c>
@@ -19307,7 +19306,7 @@
       <c r="AB277" s="2"/>
       <c r="AC277" s="2"/>
     </row>
-    <row r="278" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>335</v>
       </c>
@@ -19368,7 +19367,7 @@
       <c r="AB278" s="2"/>
       <c r="AC278" s="2"/>
     </row>
-    <row r="279" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>440</v>
       </c>
@@ -19429,7 +19428,7 @@
       <c r="AB279" s="2"/>
       <c r="AC279" s="2"/>
     </row>
-    <row r="280" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>429</v>
       </c>
@@ -19490,7 +19489,7 @@
       <c r="AB280" s="2"/>
       <c r="AC280" s="2"/>
     </row>
-    <row r="281" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>179</v>
       </c>
@@ -19551,7 +19550,7 @@
       <c r="AB281" s="2"/>
       <c r="AC281" s="2"/>
     </row>
-    <row r="282" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>473</v>
       </c>
@@ -19612,7 +19611,7 @@
       <c r="AB282" s="2"/>
       <c r="AC282" s="2"/>
     </row>
-    <row r="283" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>468</v>
       </c>
@@ -19673,7 +19672,7 @@
       <c r="AB283" s="2"/>
       <c r="AC283" s="2"/>
     </row>
-    <row r="284" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>386</v>
       </c>
@@ -19734,7 +19733,7 @@
       <c r="AB284" s="2"/>
       <c r="AC284" s="2"/>
     </row>
-    <row r="285" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>509</v>
       </c>
@@ -19795,7 +19794,7 @@
       <c r="AB285" s="2"/>
       <c r="AC285" s="2"/>
     </row>
-    <row r="286" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>372</v>
       </c>
@@ -19856,7 +19855,7 @@
       <c r="AB286" s="2"/>
       <c r="AC286" s="2"/>
     </row>
-    <row r="287" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>493</v>
       </c>
@@ -19917,7 +19916,7 @@
       <c r="AB287" s="2"/>
       <c r="AC287" s="2"/>
     </row>
-    <row r="288" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>319</v>
       </c>
@@ -19978,7 +19977,7 @@
       <c r="AB288" s="2"/>
       <c r="AC288" s="2"/>
     </row>
-    <row r="289" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>432</v>
       </c>
@@ -20039,7 +20038,7 @@
       <c r="AB289" s="2"/>
       <c r="AC289" s="2"/>
     </row>
-    <row r="290" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>341</v>
       </c>
@@ -20100,7 +20099,7 @@
       <c r="AB290" s="2"/>
       <c r="AC290" s="2"/>
     </row>
-    <row r="291" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>285</v>
       </c>
@@ -20161,7 +20160,7 @@
       <c r="AB291" s="2"/>
       <c r="AC291" s="2"/>
     </row>
-    <row r="292" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>308</v>
       </c>
@@ -20222,7 +20221,7 @@
       <c r="AB292" s="2"/>
       <c r="AC292" s="2"/>
     </row>
-    <row r="293" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>192</v>
       </c>
@@ -20283,7 +20282,7 @@
       <c r="AB293" s="2"/>
       <c r="AC293" s="2"/>
     </row>
-    <row r="294" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>431</v>
       </c>
@@ -20344,7 +20343,7 @@
       <c r="AB294" s="2"/>
       <c r="AC294" s="2"/>
     </row>
-    <row r="295" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>127</v>
       </c>
@@ -20405,7 +20404,7 @@
       <c r="AB295" s="2"/>
       <c r="AC295" s="2"/>
     </row>
-    <row r="296" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>183</v>
       </c>
@@ -20466,7 +20465,7 @@
       <c r="AB296" s="2"/>
       <c r="AC296" s="2"/>
     </row>
-    <row r="297" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>224</v>
       </c>
@@ -20527,7 +20526,7 @@
       <c r="AB297" s="2"/>
       <c r="AC297" s="2"/>
     </row>
-    <row r="298" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>430</v>
       </c>
@@ -20588,7 +20587,7 @@
       <c r="AB298" s="2"/>
       <c r="AC298" s="2"/>
     </row>
-    <row r="299" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>332</v>
       </c>
@@ -20649,7 +20648,7 @@
       <c r="AB299" s="2"/>
       <c r="AC299" s="2"/>
     </row>
-    <row r="300" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>193</v>
       </c>
@@ -20710,7 +20709,7 @@
       <c r="AB300" s="2"/>
       <c r="AC300" s="2"/>
     </row>
-    <row r="301" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>225</v>
       </c>
@@ -20771,7 +20770,7 @@
       <c r="AB301" s="2"/>
       <c r="AC301" s="2"/>
     </row>
-    <row r="302" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>437</v>
       </c>
@@ -20832,7 +20831,7 @@
       <c r="AB302" s="2"/>
       <c r="AC302" s="2"/>
     </row>
-    <row r="303" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>206</v>
       </c>
@@ -20893,7 +20892,7 @@
       <c r="AB303" s="2"/>
       <c r="AC303" s="2"/>
     </row>
-    <row r="304" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>132</v>
       </c>
@@ -20954,7 +20953,7 @@
       <c r="AB304" s="2"/>
       <c r="AC304" s="2"/>
     </row>
-    <row r="305" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>255</v>
       </c>
@@ -21015,7 +21014,7 @@
       <c r="AB305" s="2"/>
       <c r="AC305" s="2"/>
     </row>
-    <row r="306" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>293</v>
       </c>
@@ -21076,7 +21075,7 @@
       <c r="AB306" s="2"/>
       <c r="AC306" s="2"/>
     </row>
-    <row r="307" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>370</v>
       </c>
@@ -21137,7 +21136,7 @@
       <c r="AB307" s="2"/>
       <c r="AC307" s="2"/>
     </row>
-    <row r="308" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>236</v>
       </c>
@@ -21198,7 +21197,7 @@
       <c r="AB308" s="2"/>
       <c r="AC308" s="2"/>
     </row>
-    <row r="309" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>403</v>
       </c>
@@ -21259,7 +21258,7 @@
       <c r="AB309" s="2"/>
       <c r="AC309" s="2"/>
     </row>
-    <row r="310" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>178</v>
       </c>
@@ -21320,7 +21319,7 @@
       <c r="AB310" s="2"/>
       <c r="AC310" s="2"/>
     </row>
-    <row r="311" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>175</v>
       </c>
@@ -21381,7 +21380,7 @@
       <c r="AB311" s="2"/>
       <c r="AC311" s="2"/>
     </row>
-    <row r="312" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>136</v>
       </c>
@@ -21442,7 +21441,7 @@
       <c r="AB312" s="2"/>
       <c r="AC312" s="2"/>
     </row>
-    <row r="313" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>349</v>
       </c>
@@ -21503,7 +21502,7 @@
       <c r="AB313" s="2"/>
       <c r="AC313" s="2"/>
     </row>
-    <row r="314" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>163</v>
       </c>
@@ -21564,7 +21563,7 @@
       <c r="AB314" s="2"/>
       <c r="AC314" s="2"/>
     </row>
-    <row r="315" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>445</v>
       </c>
@@ -21625,7 +21624,7 @@
       <c r="AB315" s="2"/>
       <c r="AC315" s="2"/>
     </row>
-    <row r="316" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>241</v>
       </c>
@@ -21686,7 +21685,7 @@
       <c r="AB316" s="2"/>
       <c r="AC316" s="2"/>
     </row>
-    <row r="317" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>517</v>
       </c>
@@ -21747,7 +21746,7 @@
       <c r="AB317" s="2"/>
       <c r="AC317" s="2"/>
     </row>
-    <row r="318" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>324</v>
       </c>
@@ -21808,7 +21807,7 @@
       <c r="AB318" s="2"/>
       <c r="AC318" s="2"/>
     </row>
-    <row r="319" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>251</v>
       </c>
@@ -21869,7 +21868,7 @@
       <c r="AB319" s="2"/>
       <c r="AC319" s="2"/>
     </row>
-    <row r="320" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>448</v>
       </c>
@@ -21930,7 +21929,7 @@
       <c r="AB320" s="2"/>
       <c r="AC320" s="2"/>
     </row>
-    <row r="321" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>495</v>
       </c>
@@ -21991,7 +21990,7 @@
       <c r="AB321" s="2"/>
       <c r="AC321" s="2"/>
     </row>
-    <row r="322" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>270</v>
       </c>
@@ -22052,7 +22051,7 @@
       <c r="AB322" s="2"/>
       <c r="AC322" s="2"/>
     </row>
-    <row r="323" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>245</v>
       </c>
@@ -22113,7 +22112,7 @@
       <c r="AB323" s="2"/>
       <c r="AC323" s="2"/>
     </row>
-    <row r="324" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>99</v>
       </c>
@@ -22174,7 +22173,7 @@
       <c r="AB324" s="2"/>
       <c r="AC324" s="2"/>
     </row>
-    <row r="325" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>168</v>
       </c>
@@ -22235,7 +22234,7 @@
       <c r="AB325" s="2"/>
       <c r="AC325" s="2"/>
     </row>
-    <row r="326" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>330</v>
       </c>
@@ -22296,7 +22295,7 @@
       <c r="AB326" s="2"/>
       <c r="AC326" s="2"/>
     </row>
-    <row r="327" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>195</v>
       </c>
@@ -22357,7 +22356,7 @@
       <c r="AB327" s="2"/>
       <c r="AC327" s="2"/>
     </row>
-    <row r="328" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>304</v>
       </c>
@@ -22418,7 +22417,7 @@
       <c r="AB328" s="2"/>
       <c r="AC328" s="2"/>
     </row>
-    <row r="329" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>428</v>
       </c>
@@ -22479,7 +22478,7 @@
       <c r="AB329" s="2"/>
       <c r="AC329" s="2"/>
     </row>
-    <row r="330" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>419</v>
       </c>
@@ -22540,7 +22539,7 @@
       <c r="AB330" s="2"/>
       <c r="AC330" s="2"/>
     </row>
-    <row r="331" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>393</v>
       </c>
@@ -22601,7 +22600,7 @@
       <c r="AB331" s="2"/>
       <c r="AC331" s="2"/>
     </row>
-    <row r="332" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>425</v>
       </c>
@@ -22662,7 +22661,7 @@
       <c r="AB332" s="2"/>
       <c r="AC332" s="2"/>
     </row>
-    <row r="333" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>326</v>
       </c>
@@ -22723,7 +22722,7 @@
       <c r="AB333" s="2"/>
       <c r="AC333" s="2"/>
     </row>
-    <row r="334" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>338</v>
       </c>
@@ -22784,7 +22783,7 @@
       <c r="AB334" s="2"/>
       <c r="AC334" s="2"/>
     </row>
-    <row r="335" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>381</v>
       </c>
@@ -22845,7 +22844,7 @@
       <c r="AB335" s="2"/>
       <c r="AC335" s="2"/>
     </row>
-    <row r="336" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>347</v>
       </c>
@@ -22906,7 +22905,7 @@
       <c r="AB336" s="2"/>
       <c r="AC336" s="2"/>
     </row>
-    <row r="337" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>74</v>
       </c>
@@ -22967,7 +22966,7 @@
       <c r="AB337" s="2"/>
       <c r="AC337" s="2"/>
     </row>
-    <row r="338" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>385</v>
       </c>
@@ -23028,7 +23027,7 @@
       <c r="AB338" s="2"/>
       <c r="AC338" s="2"/>
     </row>
-    <row r="339" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>144</v>
       </c>
@@ -23089,7 +23088,7 @@
       <c r="AB339" s="2"/>
       <c r="AC339" s="2"/>
     </row>
-    <row r="340" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>379</v>
       </c>
@@ -23150,7 +23149,7 @@
       <c r="AB340" s="2"/>
       <c r="AC340" s="2"/>
     </row>
-    <row r="341" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>444</v>
       </c>
@@ -23211,7 +23210,7 @@
       <c r="AB341" s="2"/>
       <c r="AC341" s="2"/>
     </row>
-    <row r="342" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>93</v>
       </c>
@@ -23272,7 +23271,7 @@
       <c r="AB342" s="2"/>
       <c r="AC342" s="2"/>
     </row>
-    <row r="343" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>322</v>
       </c>
@@ -23333,7 +23332,7 @@
       <c r="AB343" s="2"/>
       <c r="AC343" s="2"/>
     </row>
-    <row r="344" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>421</v>
       </c>
@@ -23394,7 +23393,7 @@
       <c r="AB344" s="2"/>
       <c r="AC344" s="2"/>
     </row>
-    <row r="345" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>278</v>
       </c>
@@ -23455,7 +23454,7 @@
       <c r="AB345" s="2"/>
       <c r="AC345" s="2"/>
     </row>
-    <row r="346" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>340</v>
       </c>
@@ -23516,7 +23515,7 @@
       <c r="AB346" s="2"/>
       <c r="AC346" s="2"/>
     </row>
-    <row r="347" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>452</v>
       </c>
@@ -23577,7 +23576,7 @@
       <c r="AB347" s="2"/>
       <c r="AC347" s="2"/>
     </row>
-    <row r="348" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>469</v>
       </c>
@@ -23638,7 +23637,7 @@
       <c r="AB348" s="2"/>
       <c r="AC348" s="2"/>
     </row>
-    <row r="349" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>71</v>
       </c>
@@ -23699,7 +23698,7 @@
       <c r="AB349" s="2"/>
       <c r="AC349" s="2"/>
     </row>
-    <row r="350" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>491</v>
       </c>
@@ -23760,7 +23759,7 @@
       <c r="AB350" s="2"/>
       <c r="AC350" s="2"/>
     </row>
-    <row r="351" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>400</v>
       </c>
@@ -23821,7 +23820,7 @@
       <c r="AB351" s="2"/>
       <c r="AC351" s="2"/>
     </row>
-    <row r="352" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>223</v>
       </c>
@@ -23882,7 +23881,7 @@
       <c r="AB352" s="2"/>
       <c r="AC352" s="2"/>
     </row>
-    <row r="353" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>197</v>
       </c>
@@ -23943,7 +23942,7 @@
       <c r="AB353" s="2"/>
       <c r="AC353" s="2"/>
     </row>
-    <row r="354" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>449</v>
       </c>
@@ -24004,7 +24003,7 @@
       <c r="AB354" s="2"/>
       <c r="AC354" s="2"/>
     </row>
-    <row r="355" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>246</v>
       </c>
@@ -24065,7 +24064,7 @@
       <c r="AB355" s="2"/>
       <c r="AC355" s="2"/>
     </row>
-    <row r="356" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>524</v>
       </c>
@@ -24126,7 +24125,7 @@
       <c r="AB356" s="2"/>
       <c r="AC356" s="2"/>
     </row>
-    <row r="357" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>262</v>
       </c>
@@ -24187,7 +24186,7 @@
       <c r="AB357" s="2"/>
       <c r="AC357" s="2"/>
     </row>
-    <row r="358" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>51</v>
       </c>
@@ -24248,7 +24247,7 @@
       <c r="AB358" s="2"/>
       <c r="AC358" s="2"/>
     </row>
-    <row r="359" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>309</v>
       </c>
@@ -24309,7 +24308,7 @@
       <c r="AB359" s="2"/>
       <c r="AC359" s="2"/>
     </row>
-    <row r="360" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>47</v>
       </c>
@@ -24370,7 +24369,7 @@
       <c r="AB360" s="2"/>
       <c r="AC360" s="2"/>
     </row>
-    <row r="361" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>122</v>
       </c>
@@ -24431,7 +24430,7 @@
       <c r="AB361" s="2"/>
       <c r="AC361" s="2"/>
     </row>
-    <row r="362" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>542</v>
       </c>
@@ -24492,7 +24491,7 @@
       <c r="AB362" s="2"/>
       <c r="AC362" s="2"/>
     </row>
-    <row r="363" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>83</v>
       </c>
@@ -24553,7 +24552,7 @@
       <c r="AB363" s="2"/>
       <c r="AC363" s="2"/>
     </row>
-    <row r="364" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>472</v>
       </c>
@@ -24614,7 +24613,7 @@
       <c r="AB364" s="2"/>
       <c r="AC364" s="2"/>
     </row>
-    <row r="365" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>257</v>
       </c>
@@ -24675,7 +24674,7 @@
       <c r="AB365" s="2"/>
       <c r="AC365" s="2"/>
     </row>
-    <row r="366" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>339</v>
       </c>
@@ -24736,7 +24735,7 @@
       <c r="AB366" s="2"/>
       <c r="AC366" s="2"/>
     </row>
-    <row r="367" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>98</v>
       </c>
@@ -24797,7 +24796,7 @@
       <c r="AB367" s="2"/>
       <c r="AC367" s="2"/>
     </row>
-    <row r="368" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>540</v>
       </c>
@@ -24858,7 +24857,7 @@
       <c r="AB368" s="2"/>
       <c r="AC368" s="2"/>
     </row>
-    <row r="369" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>89</v>
       </c>
@@ -24919,7 +24918,7 @@
       <c r="AB369" s="2"/>
       <c r="AC369" s="2"/>
     </row>
-    <row r="370" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>489</v>
       </c>
@@ -24980,7 +24979,7 @@
       <c r="AB370" s="2"/>
       <c r="AC370" s="2"/>
     </row>
-    <row r="371" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>227</v>
       </c>
@@ -25041,7 +25040,7 @@
       <c r="AB371" s="2"/>
       <c r="AC371" s="2"/>
     </row>
-    <row r="372" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>173</v>
       </c>
@@ -25102,7 +25101,7 @@
       <c r="AB372" s="2"/>
       <c r="AC372" s="2"/>
     </row>
-    <row r="373" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>292</v>
       </c>
@@ -25163,7 +25162,7 @@
       <c r="AB373" s="2"/>
       <c r="AC373" s="2"/>
     </row>
-    <row r="374" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>39</v>
       </c>
@@ -25224,7 +25223,7 @@
       <c r="AB374" s="2"/>
       <c r="AC374" s="2"/>
     </row>
-    <row r="375" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>329</v>
       </c>
@@ -25285,7 +25284,7 @@
       <c r="AB375" s="2"/>
       <c r="AC375" s="2"/>
     </row>
-    <row r="376" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>378</v>
       </c>
@@ -25346,7 +25345,7 @@
       <c r="AB376" s="2"/>
       <c r="AC376" s="2"/>
     </row>
-    <row r="377" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>383</v>
       </c>
@@ -25407,7 +25406,7 @@
       <c r="AB377" s="2"/>
       <c r="AC377" s="2"/>
     </row>
-    <row r="378" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>310</v>
       </c>
@@ -25468,7 +25467,7 @@
       <c r="AB378" s="2"/>
       <c r="AC378" s="2"/>
     </row>
-    <row r="379" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>391</v>
       </c>
@@ -25529,7 +25528,7 @@
       <c r="AB379" s="2"/>
       <c r="AC379" s="2"/>
     </row>
-    <row r="380" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>396</v>
       </c>
@@ -25590,7 +25589,7 @@
       <c r="AB380" s="2"/>
       <c r="AC380" s="2"/>
     </row>
-    <row r="381" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>366</v>
       </c>
@@ -25651,7 +25650,7 @@
       <c r="AB381" s="2"/>
       <c r="AC381" s="2"/>
     </row>
-    <row r="382" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>457</v>
       </c>
@@ -25712,7 +25711,7 @@
       <c r="AB382" s="2"/>
       <c r="AC382" s="2"/>
     </row>
-    <row r="383" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>48</v>
       </c>
@@ -25773,7 +25772,7 @@
       <c r="AB383" s="2"/>
       <c r="AC383" s="2"/>
     </row>
-    <row r="384" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>520</v>
       </c>
@@ -25834,7 +25833,7 @@
       <c r="AB384" s="2"/>
       <c r="AC384" s="2"/>
     </row>
-    <row r="385" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>267</v>
       </c>
@@ -25895,7 +25894,7 @@
       <c r="AB385" s="2"/>
       <c r="AC385" s="2"/>
     </row>
-    <row r="386" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>464</v>
       </c>
@@ -25956,7 +25955,7 @@
       <c r="AB386" s="2"/>
       <c r="AC386" s="2"/>
     </row>
-    <row r="387" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>423</v>
       </c>
@@ -26017,7 +26016,7 @@
       <c r="AB387" s="2"/>
       <c r="AC387" s="2"/>
     </row>
-    <row r="388" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>162</v>
       </c>
@@ -26078,7 +26077,7 @@
       <c r="AB388" s="2"/>
       <c r="AC388" s="2"/>
     </row>
-    <row r="389" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>209</v>
       </c>
@@ -26139,7 +26138,7 @@
       <c r="AB389" s="2"/>
       <c r="AC389" s="2"/>
     </row>
-    <row r="390" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>458</v>
       </c>
@@ -26200,7 +26199,7 @@
       <c r="AB390" s="2"/>
       <c r="AC390" s="2"/>
     </row>
-    <row r="391" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>242</v>
       </c>
@@ -26261,7 +26260,7 @@
       <c r="AB391" s="2"/>
       <c r="AC391" s="2"/>
     </row>
-    <row r="392" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>484</v>
       </c>
@@ -26322,7 +26321,7 @@
       <c r="AB392" s="2"/>
       <c r="AC392" s="2"/>
     </row>
-    <row r="393" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>218</v>
       </c>
@@ -26383,7 +26382,7 @@
       <c r="AB393" s="2"/>
       <c r="AC393" s="2"/>
     </row>
-    <row r="394" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>496</v>
       </c>
@@ -26444,7 +26443,7 @@
       <c r="AB394" s="2"/>
       <c r="AC394" s="2"/>
     </row>
-    <row r="395" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>365</v>
       </c>
@@ -26505,7 +26504,7 @@
       <c r="AB395" s="2"/>
       <c r="AC395" s="2"/>
     </row>
-    <row r="396" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>281</v>
       </c>
@@ -26566,7 +26565,7 @@
       <c r="AB396" s="2"/>
       <c r="AC396" s="2"/>
     </row>
-    <row r="397" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>405</v>
       </c>
@@ -26627,7 +26626,7 @@
       <c r="AB397" s="2"/>
       <c r="AC397" s="2"/>
     </row>
-    <row r="398" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>205</v>
       </c>
@@ -26688,7 +26687,7 @@
       <c r="AB398" s="2"/>
       <c r="AC398" s="2"/>
     </row>
-    <row r="399" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>189</v>
       </c>
@@ -26749,7 +26748,7 @@
       <c r="AB399" s="2"/>
       <c r="AC399" s="2"/>
     </row>
-    <row r="400" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>305</v>
       </c>
@@ -26810,7 +26809,7 @@
       <c r="AB400" s="2"/>
       <c r="AC400" s="2"/>
     </row>
-    <row r="401" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>409</v>
       </c>
@@ -26871,7 +26870,7 @@
       <c r="AB401" s="2"/>
       <c r="AC401" s="2"/>
     </row>
-    <row r="402" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>263</v>
       </c>
@@ -26932,7 +26931,7 @@
       <c r="AB402" s="2"/>
       <c r="AC402" s="2"/>
     </row>
-    <row r="403" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>87</v>
       </c>
@@ -26993,7 +26992,7 @@
       <c r="AB403" s="2"/>
       <c r="AC403" s="2"/>
     </row>
-    <row r="404" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>158</v>
       </c>
@@ -27054,7 +27053,7 @@
       <c r="AB404" s="2"/>
       <c r="AC404" s="2"/>
     </row>
-    <row r="405" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>29</v>
       </c>
@@ -27115,7 +27114,7 @@
       <c r="AB405" s="2"/>
       <c r="AC405" s="2"/>
     </row>
-    <row r="406" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>456</v>
       </c>
@@ -27176,7 +27175,7 @@
       <c r="AB406" s="2"/>
       <c r="AC406" s="2"/>
     </row>
-    <row r="407" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>413</v>
       </c>
@@ -27237,7 +27236,7 @@
       <c r="AB407" s="2"/>
       <c r="AC407" s="2"/>
     </row>
-    <row r="408" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>180</v>
       </c>
@@ -27298,7 +27297,7 @@
       <c r="AB408" s="2"/>
       <c r="AC408" s="2"/>
     </row>
-    <row r="409" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>453</v>
       </c>
@@ -27359,7 +27358,7 @@
       <c r="AB409" s="2"/>
       <c r="AC409" s="2"/>
     </row>
-    <row r="410" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>351</v>
       </c>
@@ -27420,7 +27419,7 @@
       <c r="AB410" s="2"/>
       <c r="AC410" s="2"/>
     </row>
-    <row r="411" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>86</v>
       </c>
@@ -27481,7 +27480,7 @@
       <c r="AB411" s="2"/>
       <c r="AC411" s="2"/>
     </row>
-    <row r="412" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>95</v>
       </c>
@@ -27542,7 +27541,7 @@
       <c r="AB412" s="2"/>
       <c r="AC412" s="2"/>
     </row>
-    <row r="413" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>416</v>
       </c>
@@ -27603,7 +27602,7 @@
       <c r="AB413" s="2"/>
       <c r="AC413" s="2"/>
     </row>
-    <row r="414" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>67</v>
       </c>
@@ -27664,7 +27663,7 @@
       <c r="AB414" s="2"/>
       <c r="AC414" s="2"/>
     </row>
-    <row r="415" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>434</v>
       </c>
@@ -27725,7 +27724,7 @@
       <c r="AB415" s="2"/>
       <c r="AC415" s="2"/>
     </row>
-    <row r="416" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>143</v>
       </c>
@@ -27786,7 +27785,7 @@
       <c r="AB416" s="2"/>
       <c r="AC416" s="2"/>
     </row>
-    <row r="417" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>336</v>
       </c>
@@ -27847,7 +27846,7 @@
       <c r="AB417" s="2"/>
       <c r="AC417" s="2"/>
     </row>
-    <row r="418" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>371</v>
       </c>
@@ -27908,7 +27907,7 @@
       <c r="AB418" s="2"/>
       <c r="AC418" s="2"/>
     </row>
-    <row r="419" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>238</v>
       </c>
@@ -27969,7 +27968,7 @@
       <c r="AB419" s="2"/>
       <c r="AC419" s="2"/>
     </row>
-    <row r="420" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>228</v>
       </c>
@@ -28030,7 +28029,7 @@
       <c r="AB420" s="2"/>
       <c r="AC420" s="2"/>
     </row>
-    <row r="421" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>240</v>
       </c>
@@ -28091,7 +28090,7 @@
       <c r="AB421" s="2"/>
       <c r="AC421" s="2"/>
     </row>
-    <row r="422" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>253</v>
       </c>
@@ -28152,7 +28151,7 @@
       <c r="AB422" s="2"/>
       <c r="AC422" s="2"/>
     </row>
-    <row r="423" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>397</v>
       </c>
@@ -28213,7 +28212,7 @@
       <c r="AB423" s="2"/>
       <c r="AC423" s="2"/>
     </row>
-    <row r="424" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>358</v>
       </c>
@@ -28274,7 +28273,7 @@
       <c r="AB424" s="2"/>
       <c r="AC424" s="2"/>
     </row>
-    <row r="425" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>532</v>
       </c>
@@ -28335,7 +28334,7 @@
       <c r="AB425" s="2"/>
       <c r="AC425" s="2"/>
     </row>
-    <row r="426" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>284</v>
       </c>
@@ -28396,7 +28395,7 @@
       <c r="AB426" s="2"/>
       <c r="AC426" s="2"/>
     </row>
-    <row r="427" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>528</v>
       </c>
@@ -28457,7 +28456,7 @@
       <c r="AB427" s="2"/>
       <c r="AC427" s="2"/>
     </row>
-    <row r="428" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>256</v>
       </c>
@@ -28518,7 +28517,7 @@
       <c r="AB428" s="2"/>
       <c r="AC428" s="2"/>
     </row>
-    <row r="429" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>252</v>
       </c>
@@ -28579,7 +28578,7 @@
       <c r="AB429" s="2"/>
       <c r="AC429" s="2"/>
     </row>
-    <row r="430" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>536</v>
       </c>
@@ -28640,7 +28639,7 @@
       <c r="AB430" s="2"/>
       <c r="AC430" s="2"/>
     </row>
-    <row r="431" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>354</v>
       </c>
@@ -28701,7 +28700,7 @@
       <c r="AB431" s="2"/>
       <c r="AC431" s="2"/>
     </row>
-    <row r="432" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>359</v>
       </c>
@@ -28762,7 +28761,7 @@
       <c r="AB432" s="2"/>
       <c r="AC432" s="2"/>
     </row>
-    <row r="433" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>298</v>
       </c>
@@ -28823,7 +28822,7 @@
       <c r="AB433" s="2"/>
       <c r="AC433" s="2"/>
     </row>
-    <row r="434" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>199</v>
       </c>
@@ -28884,7 +28883,7 @@
       <c r="AB434" s="2"/>
       <c r="AC434" s="2"/>
     </row>
-    <row r="435" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>286</v>
       </c>
@@ -28945,7 +28944,7 @@
       <c r="AB435" s="2"/>
       <c r="AC435" s="2"/>
     </row>
-    <row r="436" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>427</v>
       </c>
@@ -29006,7 +29005,7 @@
       <c r="AB436" s="2"/>
       <c r="AC436" s="2"/>
     </row>
-    <row r="437" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>325</v>
       </c>
@@ -29067,7 +29066,7 @@
       <c r="AB437" s="2"/>
       <c r="AC437" s="2"/>
     </row>
-    <row r="438" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>134</v>
       </c>
@@ -29128,7 +29127,7 @@
       <c r="AB438" s="2"/>
       <c r="AC438" s="2"/>
     </row>
-    <row r="439" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>375</v>
       </c>
@@ -29189,7 +29188,7 @@
       <c r="AB439" s="2"/>
       <c r="AC439" s="2"/>
     </row>
-    <row r="440" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>507</v>
       </c>
@@ -29250,7 +29249,7 @@
       <c r="AB440" s="2"/>
       <c r="AC440" s="2"/>
     </row>
-    <row r="441" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>541</v>
       </c>
@@ -29311,7 +29310,7 @@
       <c r="AB441" s="2"/>
       <c r="AC441" s="2"/>
     </row>
-    <row r="442" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>380</v>
       </c>
@@ -29372,7 +29371,7 @@
       <c r="AB442" s="2"/>
       <c r="AC442" s="2"/>
     </row>
-    <row r="443" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>12</v>
       </c>
@@ -29433,7 +29432,7 @@
       <c r="AB443" s="2"/>
       <c r="AC443" s="2"/>
     </row>
-    <row r="444" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>231</v>
       </c>
@@ -29494,7 +29493,7 @@
       <c r="AB444" s="2"/>
       <c r="AC444" s="2"/>
     </row>
-    <row r="445" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>259</v>
       </c>
@@ -29555,7 +29554,7 @@
       <c r="AB445" s="2"/>
       <c r="AC445" s="2"/>
     </row>
-    <row r="446" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>123</v>
       </c>
@@ -29616,7 +29615,7 @@
       <c r="AB446" s="2"/>
       <c r="AC446" s="2"/>
     </row>
-    <row r="447" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>108</v>
       </c>
@@ -29677,7 +29676,7 @@
       <c r="AB447" s="2"/>
       <c r="AC447" s="2"/>
     </row>
-    <row r="448" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>494</v>
       </c>
@@ -29738,7 +29737,7 @@
       <c r="AB448" s="2"/>
       <c r="AC448" s="2"/>
     </row>
-    <row r="449" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>126</v>
       </c>
@@ -29799,7 +29798,7 @@
       <c r="AB449" s="2"/>
       <c r="AC449" s="2"/>
     </row>
-    <row r="450" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>159</v>
       </c>
@@ -29860,7 +29859,7 @@
       <c r="AB450" s="2"/>
       <c r="AC450" s="2"/>
     </row>
-    <row r="451" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>72</v>
       </c>
@@ -29921,7 +29920,7 @@
       <c r="AB451" s="2"/>
       <c r="AC451" s="2"/>
     </row>
-    <row r="452" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>368</v>
       </c>
@@ -29982,7 +29981,7 @@
       <c r="AB452" s="2"/>
       <c r="AC452" s="2"/>
     </row>
-    <row r="453" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>418</v>
       </c>
@@ -30043,7 +30042,7 @@
       <c r="AB453" s="2"/>
       <c r="AC453" s="2"/>
     </row>
-    <row r="454" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>498</v>
       </c>
@@ -30104,7 +30103,7 @@
       <c r="AB454" s="2"/>
       <c r="AC454" s="2"/>
     </row>
-    <row r="455" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>288</v>
       </c>
@@ -30165,7 +30164,7 @@
       <c r="AB455" s="2"/>
       <c r="AC455" s="2"/>
     </row>
-    <row r="456" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>77</v>
       </c>
@@ -30226,7 +30225,7 @@
       <c r="AB456" s="2"/>
       <c r="AC456" s="2"/>
     </row>
-    <row r="457" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>513</v>
       </c>
@@ -30287,7 +30286,7 @@
       <c r="AB457" s="2"/>
       <c r="AC457" s="2"/>
     </row>
-    <row r="458" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>497</v>
       </c>
@@ -30348,7 +30347,7 @@
       <c r="AB458" s="2"/>
       <c r="AC458" s="2"/>
     </row>
-    <row r="459" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>394</v>
       </c>
@@ -30409,7 +30408,7 @@
       <c r="AB459" s="2"/>
       <c r="AC459" s="2"/>
     </row>
-    <row r="460" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>43</v>
       </c>
@@ -30470,7 +30469,7 @@
       <c r="AB460" s="2"/>
       <c r="AC460" s="2"/>
     </row>
-    <row r="461" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>299</v>
       </c>
@@ -30531,7 +30530,7 @@
       <c r="AB461" s="2"/>
       <c r="AC461" s="2"/>
     </row>
-    <row r="462" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>442</v>
       </c>
@@ -30592,7 +30591,7 @@
       <c r="AB462" s="2"/>
       <c r="AC462" s="2"/>
     </row>
-    <row r="463" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>222</v>
       </c>
@@ -30653,7 +30652,7 @@
       <c r="AB463" s="2"/>
       <c r="AC463" s="2"/>
     </row>
-    <row r="464" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>408</v>
       </c>
@@ -30714,7 +30713,7 @@
       <c r="AB464" s="2"/>
       <c r="AC464" s="2"/>
     </row>
-    <row r="465" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>280</v>
       </c>
@@ -30775,7 +30774,7 @@
       <c r="AB465" s="2"/>
       <c r="AC465" s="2"/>
     </row>
-    <row r="466" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>156</v>
       </c>
@@ -30836,7 +30835,7 @@
       <c r="AB466" s="2"/>
       <c r="AC466" s="2"/>
     </row>
-    <row r="467" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>516</v>
       </c>
@@ -30897,7 +30896,7 @@
       <c r="AB467" s="2"/>
       <c r="AC467" s="2"/>
     </row>
-    <row r="468" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>234</v>
       </c>
@@ -30958,7 +30957,7 @@
       <c r="AB468" s="2"/>
       <c r="AC468" s="2"/>
     </row>
-    <row r="469" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>363</v>
       </c>
@@ -31019,7 +31018,7 @@
       <c r="AB469" s="2"/>
       <c r="AC469" s="2"/>
     </row>
-    <row r="470" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>356</v>
       </c>
@@ -31080,7 +31079,7 @@
       <c r="AB470" s="2"/>
       <c r="AC470" s="2"/>
     </row>
-    <row r="471" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>70</v>
       </c>
@@ -31141,7 +31140,7 @@
       <c r="AB471" s="2"/>
       <c r="AC471" s="2"/>
     </row>
-    <row r="472" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>461</v>
       </c>
@@ -31202,7 +31201,7 @@
       <c r="AB472" s="2"/>
       <c r="AC472" s="2"/>
     </row>
-    <row r="473" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>104</v>
       </c>
@@ -31263,7 +31262,7 @@
       <c r="AB473" s="2"/>
       <c r="AC473" s="2"/>
     </row>
-    <row r="474" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>82</v>
       </c>
@@ -31324,7 +31323,7 @@
       <c r="AB474" s="2"/>
       <c r="AC474" s="2"/>
     </row>
-    <row r="475" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>504</v>
       </c>
@@ -31385,7 +31384,7 @@
       <c r="AB475" s="2"/>
       <c r="AC475" s="2"/>
     </row>
-    <row r="476" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>404</v>
       </c>
@@ -31446,7 +31445,7 @@
       <c r="AB476" s="2"/>
       <c r="AC476" s="2"/>
     </row>
-    <row r="477" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>128</v>
       </c>
@@ -31507,7 +31506,7 @@
       <c r="AB477" s="2"/>
       <c r="AC477" s="2"/>
     </row>
-    <row r="478" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>389</v>
       </c>
@@ -31568,7 +31567,7 @@
       <c r="AB478" s="2"/>
       <c r="AC478" s="2"/>
     </row>
-    <row r="479" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>37</v>
       </c>
@@ -31629,7 +31628,7 @@
       <c r="AB479" s="2"/>
       <c r="AC479" s="2"/>
     </row>
-    <row r="480" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>185</v>
       </c>
@@ -31690,7 +31689,7 @@
       <c r="AB480" s="2"/>
       <c r="AC480" s="2"/>
     </row>
-    <row r="481" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>106</v>
       </c>
@@ -31751,7 +31750,7 @@
       <c r="AB481" s="2"/>
       <c r="AC481" s="2"/>
     </row>
-    <row r="482" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>395</v>
       </c>
@@ -31812,7 +31811,7 @@
       <c r="AB482" s="2"/>
       <c r="AC482" s="2"/>
     </row>
-    <row r="483" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>514</v>
       </c>
@@ -31873,7 +31872,7 @@
       <c r="AB483" s="2"/>
       <c r="AC483" s="2"/>
     </row>
-    <row r="484" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>478</v>
       </c>
@@ -31934,7 +31933,7 @@
       <c r="AB484" s="2"/>
       <c r="AC484" s="2"/>
     </row>
-    <row r="485" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>463</v>
       </c>
@@ -31995,7 +31994,7 @@
       <c r="AB485" s="2"/>
       <c r="AC485" s="2"/>
     </row>
-    <row r="486" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>188</v>
       </c>
@@ -32056,7 +32055,7 @@
       <c r="AB486" s="2"/>
       <c r="AC486" s="2"/>
     </row>
-    <row r="487" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>85</v>
       </c>
@@ -32117,7 +32116,7 @@
       <c r="AB487" s="2"/>
       <c r="AC487" s="2"/>
     </row>
-    <row r="488" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>521</v>
       </c>
@@ -32178,7 +32177,7 @@
       <c r="AB488" s="2"/>
       <c r="AC488" s="2"/>
     </row>
-    <row r="489" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>203</v>
       </c>
@@ -32239,7 +32238,7 @@
       <c r="AB489" s="2"/>
       <c r="AC489" s="2"/>
     </row>
-    <row r="490" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>311</v>
       </c>
@@ -32300,7 +32299,7 @@
       <c r="AB490" s="2"/>
       <c r="AC490" s="2"/>
     </row>
-    <row r="491" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>111</v>
       </c>
@@ -32361,7 +32360,7 @@
       <c r="AB491" s="2"/>
       <c r="AC491" s="2"/>
     </row>
-    <row r="492" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>481</v>
       </c>
@@ -32422,7 +32421,7 @@
       <c r="AB492" s="2"/>
       <c r="AC492" s="2"/>
     </row>
-    <row r="493" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>97</v>
       </c>
@@ -32483,7 +32482,7 @@
       <c r="AB493" s="2"/>
       <c r="AC493" s="2"/>
     </row>
-    <row r="494" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>166</v>
       </c>
@@ -32544,7 +32543,7 @@
       <c r="AB494" s="2"/>
       <c r="AC494" s="2"/>
     </row>
-    <row r="495" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>384</v>
       </c>
@@ -32605,7 +32604,7 @@
       <c r="AB495" s="2"/>
       <c r="AC495" s="2"/>
     </row>
-    <row r="496" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>360</v>
       </c>
@@ -32666,7 +32665,7 @@
       <c r="AB496" s="2"/>
       <c r="AC496" s="2"/>
     </row>
-    <row r="497" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>260</v>
       </c>
@@ -32727,7 +32726,7 @@
       <c r="AB497" s="2"/>
       <c r="AC497" s="2"/>
     </row>
-    <row r="498" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>232</v>
       </c>
@@ -32788,7 +32787,7 @@
       <c r="AB498" s="2"/>
       <c r="AC498" s="2"/>
     </row>
-    <row r="499" spans="1:29" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>346</v>
       </c>
@@ -47380,7 +47379,20 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="top10" dxfId="2" priority="1" rank="10"/>
+    <cfRule type="top10" dxfId="1" priority="2" rank="10"/>
+    <cfRule type="top10" dxfId="0" priority="3" rank="10"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFC00000"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -47391,19 +47403,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFC00000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="top10" dxfId="1" priority="3" rank="10"/>
-    <cfRule type="top10" dxfId="2" priority="2" rank="10"/>
-    <cfRule type="top10" dxfId="3" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
